--- a/PPREstimation/output/top10/34_1_Bay_of_Bengal_(1978).xlsx
+++ b/PPREstimation/output/top10/34_1_Bay_of_Bengal_(1978).xlsx
@@ -617,7 +617,6 @@
           <t>Import</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" s="2" t="n">
         <v>1</v>
       </c>
@@ -701,7 +700,6 @@
           <t>DET</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" s="2" t="n">
         <v>1</v>
       </c>
@@ -785,7 +783,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" s="2" t="n">
         <v>4.73418995058106</v>
       </c>
@@ -869,7 +866,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" s="2" t="n">
         <v>5.001329429154078</v>
       </c>
@@ -953,7 +949,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" s="2" t="n">
         <v>4.550325001365476</v>
       </c>
@@ -1037,7 +1032,6 @@
           <t>PP</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" s="2" t="n">
         <v>1</v>
       </c>
@@ -1121,7 +1115,6 @@
           <t>PP</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" s="2" t="n">
         <v>1</v>
       </c>
@@ -1205,7 +1198,6 @@
           <t>PP</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" s="2" t="n">
         <v>1</v>
       </c>
@@ -1289,7 +1281,6 @@
           <t>PP</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" s="2" t="n">
         <v>1</v>
       </c>
@@ -1373,7 +1364,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" s="2" t="n">
         <v>2</v>
       </c>
@@ -1457,7 +1447,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" s="2" t="n">
         <v>2</v>
       </c>
@@ -1541,7 +1530,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" s="2" t="n">
         <v>2.875</v>
       </c>
@@ -1625,7 +1613,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" s="2" t="n">
         <v>3.090909090909092</v>
       </c>
@@ -1709,7 +1696,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" s="2" t="n">
         <v>4.148439693062811</v>
       </c>
@@ -1793,7 +1779,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" s="2" t="n">
         <v>3.475228156388901</v>
       </c>
@@ -1877,7 +1862,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" s="2" t="n">
         <v>3.991104885765255</v>
       </c>
@@ -1961,7 +1945,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" s="2" t="n">
         <v>4.301111681085923</v>
       </c>
@@ -2045,7 +2028,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" s="2" t="n">
         <v>3.263860428527981</v>
       </c>
@@ -2129,7 +2111,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" s="2" t="n">
         <v>4.243210922747678</v>
       </c>
@@ -2213,7 +2194,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" s="2" t="n">
         <v>4.497003188381623</v>
       </c>
@@ -2297,7 +2277,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" s="2" t="n">
         <v>3.166387252038477</v>
       </c>
@@ -2381,7 +2360,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" s="2" t="n">
         <v>2.297370262973703</v>
       </c>
@@ -2465,7 +2443,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" s="2" t="n">
         <v>2</v>
       </c>
@@ -2549,7 +2526,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" s="2" t="n">
         <v>2</v>
       </c>
@@ -2633,7 +2609,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" s="2" t="n">
         <v>2.340206185567011</v>
       </c>
@@ -2717,7 +2692,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" s="2" t="n">
         <v>2.619806310527961</v>
       </c>
@@ -2801,7 +2775,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" s="2" t="n">
         <v>3.68052780739123</v>
       </c>
@@ -2885,7 +2858,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" s="2" t="n">
         <v>3.110183260661583</v>
       </c>
@@ -2969,7 +2941,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" s="2" t="n">
         <v>3.505108513298227</v>
       </c>
@@ -3053,7 +3024,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" s="2" t="n">
         <v>3.910992015654968</v>
       </c>
@@ -3137,7 +3107,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" s="2" t="n">
         <v>3.129969362591789</v>
       </c>
@@ -3221,7 +3190,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" s="2" t="n">
         <v>4.004167820379394</v>
       </c>
@@ -3305,7 +3273,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" s="2" t="n">
         <v>4.124277839527067</v>
       </c>
@@ -3389,7 +3356,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" s="2" t="n">
         <v>2</v>
       </c>
@@ -3473,7 +3439,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" s="2" t="n">
         <v>2</v>
       </c>
@@ -3557,7 +3522,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" s="2" t="n">
         <v>2.368421052631579</v>
       </c>
@@ -3641,7 +3605,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" s="2" t="n">
         <v>3.598063139386938</v>
       </c>
@@ -3725,7 +3688,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" s="2" t="n">
         <v>3.082457344013956</v>
       </c>
@@ -3809,7 +3771,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" s="2" t="n">
         <v>3.846894543756985</v>
       </c>
@@ -3893,7 +3854,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
       <c r="F41" s="2" t="n">
         <v>3.096219530959615</v>
       </c>
@@ -3977,7 +3937,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
       <c r="F42" s="2" t="n">
         <v>3.976872614219186</v>
       </c>
@@ -4061,7 +4020,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" s="2" t="n">
         <v>4.099224098345555</v>
       </c>
@@ -4145,7 +4103,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
       <c r="F44" s="2" t="n">
         <v>3.596999541632769</v>
       </c>
@@ -4229,7 +4186,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
       <c r="F45" s="2" t="n">
         <v>3</v>
       </c>
@@ -4313,7 +4269,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
       <c r="F46" s="2" t="n">
         <v>4.138063348144405</v>
       </c>
@@ -4397,7 +4352,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
       <c r="F47" s="2" t="n">
         <v>3</v>
       </c>
@@ -4481,7 +4435,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
       <c r="F48" s="2" t="n">
         <v>4.435912251105862</v>
       </c>
@@ -4565,7 +4518,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" s="2" t="n">
         <v>4.71341587801659</v>
       </c>
@@ -4649,7 +4601,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
       <c r="F50" s="2" t="n">
         <v>4.256960153149342</v>
       </c>
@@ -4733,7 +4684,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
       <c r="F51" s="2" t="n">
         <v>4.358975082998549</v>
       </c>
@@ -4809,7 +4759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V51"/>
+  <dimension ref="A1:X51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4947,6 +4897,16 @@
           <t>MC_new_TE_EEfix</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -4957,9 +4917,6 @@
           <t>diet_import</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
@@ -4990,19 +4947,19 @@
       <c r="O2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5015,9 +4972,6 @@
           <t>Detritus</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
@@ -5067,6 +5021,9 @@
         <v>0</v>
       </c>
       <c r="V3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5079,11 +5036,8 @@
           <t>Marlins</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" s="2" t="n">
-        <v>474.6964950739924</v>
+        <v>5989.447934060278</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>1542.438431221304</v>
@@ -5132,6 +5086,9 @@
       </c>
       <c r="V4" s="2" t="n">
         <v>6271.847616742222</v>
+      </c>
+      <c r="X4" t="n">
+        <v>474.6964950739924</v>
       </c>
     </row>
     <row r="5">
@@ -5143,11 +5100,8 @@
           <t>Yellowfin tuna</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" s="2" t="n">
-        <v>381.2516158458334</v>
+        <v>3727.58252775418</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>1066.791080581652</v>
@@ -5196,6 +5150,9 @@
       </c>
       <c r="V5" s="2" t="n">
         <v>3792.811864997067</v>
+      </c>
+      <c r="X5" t="n">
+        <v>381.2516158458334</v>
       </c>
     </row>
     <row r="6">
@@ -5207,11 +5164,8 @@
           <t>Bigeye tuna</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" s="2" t="n">
-        <v>383.2200186050479</v>
+        <v>4755.043772970804</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>1527.369786745469</v>
@@ -5260,6 +5214,9 @@
       </c>
       <c r="V6" s="2" t="n">
         <v>5182.34391764457</v>
+      </c>
+      <c r="X6" t="n">
+        <v>383.2200186050479</v>
       </c>
     </row>
     <row r="7">
@@ -5271,9 +5228,6 @@
           <t>Benthic plants</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" s="2" t="n">
         <v>1</v>
       </c>
@@ -5323,6 +5277,9 @@
         <v>1</v>
       </c>
       <c r="V7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5335,9 +5292,6 @@
           <t>3 Phytoplankton</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" s="2" t="n">
         <v>1</v>
       </c>
@@ -5387,6 +5341,9 @@
         <v>1</v>
       </c>
       <c r="V8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5399,9 +5356,6 @@
           <t>2 Phytoplankton</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" s="2" t="n">
         <v>1</v>
       </c>
@@ -5451,6 +5405,9 @@
         <v>1</v>
       </c>
       <c r="V9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5463,9 +5420,6 @@
           <t>1 Phytoplankton</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" s="2" t="n">
         <v>1</v>
       </c>
@@ -5515,6 +5469,9 @@
         <v>1</v>
       </c>
       <c r="V10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5527,11 +5484,8 @@
           <t>3 Zooplankton</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" s="2" t="n">
-        <v>5.184929654305977</v>
+        <v>8.452571931857362</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>7.77777777777778</v>
@@ -5580,6 +5534,9 @@
       </c>
       <c r="V11" s="2" t="n">
         <v>7.830316843609689</v>
+      </c>
+      <c r="X11" t="n">
+        <v>5.184929654305977</v>
       </c>
     </row>
     <row r="12">
@@ -5591,9 +5548,6 @@
           <t>3 Meiobenthos</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" s="2" t="n">
         <v>0</v>
       </c>
@@ -5643,6 +5597,9 @@
         <v>0</v>
       </c>
       <c r="V12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5655,11 +5612,8 @@
           <t>3 Macrobenthos</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" s="2" t="n">
-        <v>7.126316705423884</v>
+        <v>17.75523204335117</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>13.77210190416406</v>
@@ -5708,6 +5662,9 @@
       </c>
       <c r="V13" s="2" t="n">
         <v>104.3709116072522</v>
+      </c>
+      <c r="X13" t="n">
+        <v>7.126316705423884</v>
       </c>
     </row>
     <row r="14">
@@ -5719,11 +5676,8 @@
           <t>3 Crustaceans</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" s="2" t="n">
-        <v>6.720873880025374</v>
+        <v>17.86149306580572</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>13.67401156430693</v>
@@ -5772,6 +5726,9 @@
       </c>
       <c r="V14" s="2" t="n">
         <v>36.86843696045937</v>
+      </c>
+      <c r="X14" t="n">
+        <v>6.720873880025374</v>
       </c>
     </row>
     <row r="15">
@@ -5783,11 +5740,8 @@
           <t>3 SM pisc</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" s="2" t="n">
-        <v>53.67496423126295</v>
+        <v>270.855079343469</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>99.24366313744545</v>
@@ -5836,6 +5790,9 @@
       </c>
       <c r="V15" s="2" t="n">
         <v>708.5733992358092</v>
+      </c>
+      <c r="X15" t="n">
+        <v>53.67496423126295</v>
       </c>
     </row>
     <row r="16">
@@ -5847,11 +5804,8 @@
           <t>3 SM inv</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" s="2" t="n">
-        <v>27.77405531179006</v>
+        <v>107.454468962628</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>51.19910532920201</v>
@@ -5900,6 +5854,9 @@
       </c>
       <c r="V16" s="2" t="n">
         <v>286.8977963107839</v>
+      </c>
+      <c r="X16" t="n">
+        <v>27.77405531179006</v>
       </c>
     </row>
     <row r="17">
@@ -5911,11 +5868,8 @@
           <t>3 Milkfish plus</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" s="2" t="n">
-        <v>46.80825930700499</v>
+        <v>253.3751955992873</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>104.0935377540855</v>
@@ -5964,6 +5918,9 @@
       </c>
       <c r="V17" s="2" t="n">
         <v>822.5517688602871</v>
+      </c>
+      <c r="X17" t="n">
+        <v>46.80825930700499</v>
       </c>
     </row>
     <row r="18">
@@ -5975,11 +5932,8 @@
           <t>3 L pisc comm</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" s="2" t="n">
-        <v>126.4783827237244</v>
+        <v>981.2877690289579</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>336.548974645624</v>
@@ -6028,6 +5982,9 @@
       </c>
       <c r="V18" s="2" t="n">
         <v>1855.377275900566</v>
+      </c>
+      <c r="X18" t="n">
+        <v>126.4783827237244</v>
       </c>
     </row>
     <row r="19">
@@ -6039,11 +5996,8 @@
           <t>3 S pelagics</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" s="2" t="n">
-        <v>29.10061461489171</v>
+        <v>99.30911991403558</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>40.5038835527486</v>
@@ -6092,6 +6046,9 @@
       </c>
       <c r="V19" s="2" t="n">
         <v>161.3779072220794</v>
+      </c>
+      <c r="X19" t="n">
+        <v>29.10061461489171</v>
       </c>
     </row>
     <row r="20">
@@ -6103,11 +6060,8 @@
           <t>3 Carangids</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" s="2" t="n">
-        <v>134.5896466525014</v>
+        <v>936.0048772274749</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>367.8935933804602</v>
@@ -6156,6 +6110,9 @@
       </c>
       <c r="V20" s="2" t="n">
         <v>1598.976118481778</v>
+      </c>
+      <c r="X20" t="n">
+        <v>134.5896466525014</v>
       </c>
     </row>
     <row r="21">
@@ -6167,11 +6124,8 @@
           <t>3 L pisc</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" s="2" t="n">
-        <v>231.3998693695281</v>
+        <v>2133.921725173991</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>590.2039389237995</v>
@@ -6220,6 +6174,9 @@
       </c>
       <c r="V21" s="2" t="n">
         <v>3046.908037249639</v>
+      </c>
+      <c r="X21" t="n">
+        <v>231.3998693695281</v>
       </c>
     </row>
     <row r="22">
@@ -6231,11 +6188,8 @@
           <t>2-3 Indian mackerel</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" s="2" t="n">
-        <v>22.26331708168662</v>
+        <v>81.6744660989215</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>50.24390172473094</v>
@@ -6284,6 +6238,9 @@
       </c>
       <c r="V22" s="2" t="n">
         <v>199.1821169207439</v>
+      </c>
+      <c r="X22" t="n">
+        <v>22.26331708168662</v>
       </c>
     </row>
     <row r="23">
@@ -6295,11 +6252,8 @@
           <t>2-3 Hilsa</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" s="2" t="n">
-        <v>9.909915656073711</v>
+        <v>23.56006382491007</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>21.10354904419437</v>
@@ -6348,6 +6302,9 @@
       </c>
       <c r="V23" s="2" t="n">
         <v>20.84177273475689</v>
+      </c>
+      <c r="X23" t="n">
+        <v>9.909915656073711</v>
       </c>
     </row>
     <row r="24">
@@ -6359,11 +6316,8 @@
           <t>2 Zooplankton</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" s="2" t="n">
-        <v>4.666436688875379</v>
+        <v>7.607314738671626</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>14.94661921708185</v>
@@ -6412,6 +6366,9 @@
       </c>
       <c r="V24" s="2" t="n">
         <v>14.78065741786261</v>
+      </c>
+      <c r="X24" t="n">
+        <v>4.666436688875379</v>
       </c>
     </row>
     <row r="25">
@@ -6423,9 +6380,6 @@
           <t>2 Meiobenthos</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" s="2" t="n">
         <v>0</v>
       </c>
@@ -6475,6 +6429,9 @@
         <v>0</v>
       </c>
       <c r="V25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6487,11 +6444,8 @@
           <t>2 Macrobenthos</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" s="2" t="n">
-        <v>3.041706155325852</v>
+        <v>7.444446135512944</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>12.71141168116904</v>
@@ -6540,6 +6494,9 @@
       </c>
       <c r="V26" s="2" t="n">
         <v>16.58432174673912</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3.041706155325852</v>
       </c>
     </row>
     <row r="27">
@@ -6551,11 +6508,8 @@
           <t>2 Crustaceans</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" s="2" t="n">
-        <v>4.260113192991063</v>
+        <v>12.16219491366552</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>20.55642264431269</v>
@@ -6604,6 +6558,9 @@
       </c>
       <c r="V27" s="2" t="n">
         <v>23.5494743211912</v>
+      </c>
+      <c r="X27" t="n">
+        <v>4.260113192991063</v>
       </c>
     </row>
     <row r="28">
@@ -6615,11 +6572,8 @@
           <t>2 SM pisc</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" s="2" t="n">
-        <v>36.29224856616739</v>
+        <v>182.8017510568849</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>129.0414640524525</v>
@@ -6668,6 +6622,9 @@
       </c>
       <c r="V28" s="2" t="n">
         <v>299.811528010481</v>
+      </c>
+      <c r="X28" t="n">
+        <v>36.29224856616739</v>
       </c>
     </row>
     <row r="29">
@@ -6679,11 +6636,8 @@
           <t>2 SM inv</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" s="2" t="n">
-        <v>15.35990933529989</v>
+        <v>58.1268788346426</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>55.02839686287678</v>
@@ -6732,6 +6686,9 @@
       </c>
       <c r="V29" s="2" t="n">
         <v>96.05006742227296</v>
+      </c>
+      <c r="X29" t="n">
+        <v>15.35990933529989</v>
       </c>
     </row>
     <row r="30">
@@ -6743,11 +6700,8 @@
           <t>2 Milkfish plus</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" s="2" t="n">
-        <v>28.10442124085429</v>
+        <v>173.5100799924585</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>104.3204094001796</v>
@@ -6796,6 +6750,9 @@
       </c>
       <c r="V30" s="2" t="n">
         <v>310.171642437693</v>
+      </c>
+      <c r="X30" t="n">
+        <v>28.10442124085429</v>
       </c>
     </row>
     <row r="31">
@@ -6807,11 +6764,8 @@
           <t>2 L pisc comm</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" s="2" t="n">
-        <v>82.42737501659659</v>
+        <v>605.6263136731094</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>358.8205995588806</v>
@@ -6860,6 +6814,9 @@
       </c>
       <c r="V31" s="2" t="n">
         <v>863.9048552399403</v>
+      </c>
+      <c r="X31" t="n">
+        <v>82.42737501659659</v>
       </c>
     </row>
     <row r="32">
@@ -6871,11 +6828,8 @@
           <t>2 S pelagics</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" s="2" t="n">
-        <v>23.61015942728857</v>
+        <v>78.40215338205834</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>64.2036847684294</v>
@@ -6924,6 +6878,9 @@
       </c>
       <c r="V32" s="2" t="n">
         <v>113.6103451990135</v>
+      </c>
+      <c r="X32" t="n">
+        <v>23.61015942728857</v>
       </c>
     </row>
     <row r="33">
@@ -6935,11 +6892,8 @@
           <t>2 Carangids</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" s="2" t="n">
-        <v>103.543798898715</v>
+        <v>730.0936120294521</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>383.2136289815373</v>
@@ -6988,6 +6942,9 @@
       </c>
       <c r="V33" s="2" t="n">
         <v>994.8812878802662</v>
+      </c>
+      <c r="X33" t="n">
+        <v>103.543798898715</v>
       </c>
     </row>
     <row r="34">
@@ -6999,11 +6956,8 @@
           <t>2 L pisc</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" s="2" t="n">
-        <v>136.1797806903168</v>
+        <v>1137.517597397449</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>528.1110491756449</v>
@@ -7052,6 +7006,9 @@
       </c>
       <c r="V34" s="2" t="n">
         <v>1349.556572270131</v>
+      </c>
+      <c r="X34" t="n">
+        <v>136.1797806903168</v>
       </c>
     </row>
     <row r="35">
@@ -7063,11 +7020,8 @@
           <t>1 Zooplankton</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" s="2" t="n">
-        <v>4.666436688875379</v>
+        <v>7.607314738671626</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>7.000000000000001</v>
@@ -7116,6 +7070,9 @@
       </c>
       <c r="V35" s="2" t="n">
         <v>7.004727728324195</v>
+      </c>
+      <c r="X35" t="n">
+        <v>4.666436688875379</v>
       </c>
     </row>
     <row r="36">
@@ -7127,9 +7084,6 @@
           <t>1 Meiobenthos</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" s="2" t="n">
         <v>0</v>
       </c>
@@ -7179,6 +7133,9 @@
         <v>0</v>
       </c>
       <c r="V36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7191,11 +7148,8 @@
           <t>1 Macrobenthos</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" s="2" t="n">
-        <v>2.938007562239733</v>
+        <v>7.275394696875797</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>6.665000000000001</v>
@@ -7244,6 +7198,9 @@
       </c>
       <c r="V37" s="2" t="n">
         <v>12.05014610346738</v>
+      </c>
+      <c r="X37" t="n">
+        <v>2.938007562239733</v>
       </c>
     </row>
     <row r="38">
@@ -7255,11 +7212,8 @@
           <t>1 SM pisc</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" s="2" t="n">
-        <v>38.85036337014138</v>
+        <v>205.091026202376</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>123.8150430740876</v>
@@ -7308,6 +7262,9 @@
       </c>
       <c r="V38" s="2" t="n">
         <v>295.3885608857219</v>
+      </c>
+      <c r="X38" t="n">
+        <v>38.85036337014138</v>
       </c>
     </row>
     <row r="39">
@@ -7319,11 +7276,8 @@
           <t>1 SM inv</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" s="2" t="n">
-        <v>13.7250451867163</v>
+        <v>49.38657760688845</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>29.90989042388832</v>
@@ -7372,6 +7326,9 @@
       </c>
       <c r="V39" s="2" t="n">
         <v>65.51844843717728</v>
+      </c>
+      <c r="X39" t="n">
+        <v>13.7250451867163</v>
       </c>
     </row>
     <row r="40">
@@ -7383,11 +7340,8 @@
           <t>1 L pisc comm</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" s="2" t="n">
-        <v>81.17440305144117</v>
+        <v>637.3719245236223</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>770.7715299631594</v>
@@ -7436,6 +7390,9 @@
       </c>
       <c r="V40" s="2" t="n">
         <v>2603.280799979648</v>
+      </c>
+      <c r="X40" t="n">
+        <v>81.17440305144117</v>
       </c>
     </row>
     <row r="41">
@@ -7447,11 +7404,8 @@
           <t>1 S pelagics</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
       <c r="F41" s="2" t="n">
-        <v>21.05897783330109</v>
+        <v>64.44379037218481</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>28.23107307125097</v>
@@ -7500,6 +7454,9 @@
       </c>
       <c r="V41" s="2" t="n">
         <v>60.06144370799392</v>
+      </c>
+      <c r="X41" t="n">
+        <v>21.05897783330109</v>
       </c>
     </row>
     <row r="42">
@@ -7511,11 +7468,8 @@
           <t>1 Carangids</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
       <c r="F42" s="2" t="n">
-        <v>97.07769425277836</v>
+        <v>684.7401253960679</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>275.1187718315676</v>
@@ -7564,6 +7518,9 @@
       </c>
       <c r="V42" s="2" t="n">
         <v>1075.612146139169</v>
+      </c>
+      <c r="X42" t="n">
+        <v>97.07769425277836</v>
       </c>
     </row>
     <row r="43">
@@ -7575,11 +7532,8 @@
           <t>1 L pisc</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" s="2" t="n">
-        <v>138.4783429290922</v>
+        <v>1187.365933253217</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>525.6137872438039</v>
@@ -7628,6 +7582,9 @@
       </c>
       <c r="V43" s="2" t="n">
         <v>1773.512148003017</v>
+      </c>
+      <c r="X43" t="n">
+        <v>138.4783429290922</v>
       </c>
     </row>
     <row r="44">
@@ -7639,11 +7596,8 @@
           <t>ML bathy</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
       <c r="F44" s="2" t="n">
-        <v>72.03293330652392</v>
+        <v>564.728400855662</v>
       </c>
       <c r="G44" s="2" t="n">
         <v>274.186388415577</v>
@@ -7692,6 +7646,9 @@
       </c>
       <c r="V44" s="2" t="n">
         <v>1001.903861228052</v>
+      </c>
+      <c r="X44" t="n">
+        <v>72.03293330652392</v>
       </c>
     </row>
     <row r="45">
@@ -7703,11 +7660,8 @@
           <t>S bathy</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
       <c r="F45" s="2" t="n">
-        <v>25.09520539810434</v>
+        <v>66.69338618827331</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>269.7868543082066</v>
@@ -7756,6 +7710,9 @@
       </c>
       <c r="V45" s="2" t="n">
         <v>275.199301501628</v>
+      </c>
+      <c r="X45" t="n">
+        <v>25.09520539810434</v>
       </c>
     </row>
     <row r="46">
@@ -7767,11 +7724,8 @@
           <t>Cephalopods</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
       <c r="F46" s="2" t="n">
-        <v>83.6804558441363</v>
+        <v>511.7488103945414</v>
       </c>
       <c r="G46" s="2" t="n">
         <v>216.918809018285</v>
@@ -7820,6 +7774,9 @@
       </c>
       <c r="V46" s="2" t="n">
         <v>739.327966282656</v>
+      </c>
+      <c r="X46" t="n">
+        <v>83.6804558441363</v>
       </c>
     </row>
     <row r="47">
@@ -7831,11 +7788,8 @@
           <t>Jellyfish</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
       <c r="F47" s="2" t="n">
-        <v>26.8834955201015</v>
+        <v>71.4459722632229</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>392.8170594837253</v>
@@ -7884,6 +7838,9 @@
       </c>
       <c r="V47" s="2" t="n">
         <v>405.8197911230272</v>
+      </c>
+      <c r="X47" t="n">
+        <v>26.8834955201015</v>
       </c>
     </row>
     <row r="48">
@@ -7895,11 +7852,8 @@
           <t>Coastal scombrids</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
       <c r="F48" s="2" t="n">
-        <v>232.9180615222729</v>
+        <v>2147.494806991862</v>
       </c>
       <c r="G48" s="2" t="n">
         <v>968.8972915296544</v>
@@ -7948,6 +7902,9 @@
       </c>
       <c r="V48" s="2" t="n">
         <v>3792.756934141849</v>
+      </c>
+      <c r="X48" t="n">
+        <v>232.9180615222729</v>
       </c>
     </row>
     <row r="49">
@@ -7959,11 +7916,8 @@
           <t>Tuna-like</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" s="2" t="n">
-        <v>369.9484994688661</v>
+        <v>4024.005911323157</v>
       </c>
       <c r="G49" s="2" t="n">
         <v>1217.030544452891</v>
@@ -8012,6 +7966,9 @@
       </c>
       <c r="V49" s="2" t="n">
         <v>5545.438013587435</v>
+      </c>
+      <c r="X49" t="n">
+        <v>369.9484994688661</v>
       </c>
     </row>
     <row r="50">
@@ -8023,11 +7980,8 @@
           <t>Coastal elasmobranch</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
       <c r="F50" s="2" t="n">
-        <v>269.9133817875446</v>
+        <v>3918.259862324056</v>
       </c>
       <c r="G50" s="2" t="n">
         <v>1355.349538336979</v>
@@ -8077,6 +8031,9 @@
       <c r="V50" s="2" t="n">
         <v>11319.47097121422</v>
       </c>
+      <c r="X50" t="n">
+        <v>269.9133817875446</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -8087,11 +8044,8 @@
           <t>Oceanic sharks</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
       <c r="F51" s="2" t="n">
-        <v>432.856659103337</v>
+        <v>5991.076950838909</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>2971.739047845215</v>
@@ -8140,6 +8094,9 @@
       </c>
       <c r="V51" s="2" t="n">
         <v>15378.99064862487</v>
+      </c>
+      <c r="X51" t="n">
+        <v>432.856659103337</v>
       </c>
     </row>
   </sheetData>
@@ -8153,7 +8110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V51"/>
+  <dimension ref="A1:X51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -8291,6 +8248,16 @@
           <t>MC_new_TE_EEfix</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -8340,19 +8307,22 @@
       <c r="O2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8425,6 +8395,12 @@
       <c r="V3" s="2" t="n">
         <v>0.7954499490366782</v>
       </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -8442,10 +8418,10 @@
         <v>4151.453096259821</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>385.5518078428939</v>
+        <v>2259.598482293819</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1104.537342114849</v>
+        <v>15243.03893295993</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>2731.921740310378</v>
@@ -8494,6 +8470,12 @@
       </c>
       <c r="V4" s="2" t="n">
         <v>12972.62914249565</v>
+      </c>
+      <c r="W4" t="n">
+        <v>385.5518078428939</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1104.537342114849</v>
       </c>
     </row>
     <row r="5">
@@ -8512,10 +8494,10 @@
         <v>7345.100996801307</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>579.6880360264884</v>
+        <v>3834.748855479991</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>953.6675979567884</v>
+        <v>9818.275120143719</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>1880.036795731893</v>
@@ -8564,6 +8546,12 @@
       </c>
       <c r="V5" s="2" t="n">
         <v>7808.934947892698</v>
+      </c>
+      <c r="W5" t="n">
+        <v>579.6880360264884</v>
+      </c>
+      <c r="X5" t="n">
+        <v>953.6675979567884</v>
       </c>
     </row>
     <row r="6">
@@ -8582,10 +8570,10 @@
         <v>2885.425512703825</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>297.276327018125</v>
+        <v>1612.783432435319</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>849.940410080631</v>
+        <v>11850.0136285816</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>2418.799146899335</v>
@@ -8634,6 +8622,12 @@
       </c>
       <c r="V6" s="2" t="n">
         <v>10226.97084510757</v>
+      </c>
+      <c r="W6" t="n">
+        <v>297.276327018125</v>
+      </c>
+      <c r="X6" t="n">
+        <v>849.940410080631</v>
       </c>
     </row>
     <row r="7">
@@ -8705,6 +8699,12 @@
       <c r="V7" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -8775,6 +8775,12 @@
       <c r="V8" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -8845,6 +8851,12 @@
       <c r="V9" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -8915,6 +8927,12 @@
       <c r="V10" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -8932,10 +8950,10 @@
         <v>10</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>5.184929654305977</v>
+        <v>8.452571931857362</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>5.184929654305977</v>
+        <v>8.452571931857362</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>7.77777777777778</v>
@@ -8984,6 +9002,12 @@
       </c>
       <c r="V11" s="2" t="n">
         <v>7.830316843609689</v>
+      </c>
+      <c r="W11" t="n">
+        <v>5.184929654305977</v>
+      </c>
+      <c r="X11" t="n">
+        <v>5.184929654305977</v>
       </c>
     </row>
     <row r="12">
@@ -9002,10 +9026,10 @@
         <v>10</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>5.184929654305977</v>
+        <v>8.452571931857362</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>5.184929654305977</v>
+        <v>8.452571931857362</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>7.18390804597701</v>
@@ -9054,6 +9078,12 @@
       </c>
       <c r="V12" s="2" t="n">
         <v>5.775608899396589</v>
+      </c>
+      <c r="W12" t="n">
+        <v>5.184929654305977</v>
+      </c>
+      <c r="X12" t="n">
+        <v>5.184929654305977</v>
       </c>
     </row>
     <row r="13">
@@ -9072,10 +9102,10 @@
         <v>56.2341325190349</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>17.81558222516434</v>
+        <v>41.9015927763331</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>19.07453693658011</v>
+        <v>49.50899749367245</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>36.31482653996292</v>
@@ -9124,6 +9154,12 @@
       </c>
       <c r="V13" s="2" t="n">
         <v>238.6149686923292</v>
+      </c>
+      <c r="W13" t="n">
+        <v>17.81558222516434</v>
+      </c>
+      <c r="X13" t="n">
+        <v>19.07453693658011</v>
       </c>
     </row>
     <row r="14">
@@ -9142,10 +9178,10 @@
         <v>99.99999999999999</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>26.88349552010149</v>
+        <v>71.44597226322288</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>24.64320422675971</v>
+        <v>65.49214124128767</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>47.35384300348653</v>
@@ -9194,6 +9230,12 @@
       </c>
       <c r="V14" s="2" t="n">
         <v>110.0668785531916</v>
+      </c>
+      <c r="W14" t="n">
+        <v>26.88349552010149</v>
+      </c>
+      <c r="X14" t="n">
+        <v>24.64320422675971</v>
       </c>
     </row>
     <row r="15">
@@ -9212,10 +9254,10 @@
         <v>899.5569660715325</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>129.2322560759423</v>
+        <v>547.4591457880141</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>143.7288494824836</v>
+        <v>750.0779361202104</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>230.287729400978</v>
@@ -9264,6 +9306,12 @@
       </c>
       <c r="V15" s="2" t="n">
         <v>1588.289165800089</v>
+      </c>
+      <c r="W15" t="n">
+        <v>129.2322560759425</v>
+      </c>
+      <c r="X15" t="n">
+        <v>143.7288494824836</v>
       </c>
     </row>
     <row r="16">
@@ -9282,10 +9330,10 @@
         <v>233.2691835057716</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>49.25033267370252</v>
+        <v>156.6669683960035</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>72.63063829483411</v>
+        <v>299.5915608965726</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>120.8362182834186</v>
@@ -9334,6 +9382,12 @@
       </c>
       <c r="V16" s="2" t="n">
         <v>651.8634345288813</v>
+      </c>
+      <c r="W16" t="n">
+        <v>49.25033267370252</v>
+      </c>
+      <c r="X16" t="n">
+        <v>72.63063829483411</v>
       </c>
     </row>
     <row r="17">
@@ -9352,10 +9406,10 @@
         <v>658.0386994075527</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>103.3534825911695</v>
+        <v>409.7205324309327</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>129.7631110310458</v>
+        <v>715.9641969458821</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>260.7142033034266</v>
@@ -9404,6 +9458,12 @@
       </c>
       <c r="V17" s="2" t="n">
         <v>1864.746228444168</v>
+      </c>
+      <c r="W17" t="n">
+        <v>103.3534825911695</v>
+      </c>
+      <c r="X17" t="n">
+        <v>129.7631110310458</v>
       </c>
     </row>
     <row r="18">
@@ -9422,10 +9482,10 @@
         <v>1222.123215826166</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>160.8768027173467</v>
+        <v>727.3128429368896</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>313.5701331313626</v>
+        <v>2578.698838421805</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>654.9451163749669</v>
@@ -9474,6 +9534,12 @@
       </c>
       <c r="V18" s="2" t="n">
         <v>4025.691257308343</v>
+      </c>
+      <c r="W18" t="n">
+        <v>160.8768027173467</v>
+      </c>
+      <c r="X18" t="n">
+        <v>313.5701331313626</v>
       </c>
     </row>
     <row r="19">
@@ -9492,10 +9558,10 @@
         <v>149.3209864750716</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>35.80448020290444</v>
+        <v>103.6062230671559</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>51.00296780255371</v>
+        <v>205.4335058734121</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>73.56989247513604</v>
@@ -9544,6 +9610,12 @@
       </c>
       <c r="V19" s="2" t="n">
         <v>347.6754018947128</v>
+      </c>
+      <c r="W19" t="n">
+        <v>35.80448020290444</v>
+      </c>
+      <c r="X19" t="n">
+        <v>51.00296780255371</v>
       </c>
     </row>
     <row r="20">
@@ -9562,10 +9634,10 @@
         <v>1165.755227118985</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>155.5377275061178</v>
+        <v>696.1629693121913</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>311.9107406337332</v>
+        <v>2379.613916466093</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>636.5358099618678</v>
@@ -9614,6 +9686,12 @@
       </c>
       <c r="V20" s="2" t="n">
         <v>3353.520355573446</v>
+      </c>
+      <c r="W20" t="n">
+        <v>155.5377275061178</v>
+      </c>
+      <c r="X20" t="n">
+        <v>311.9107406337332</v>
       </c>
     </row>
     <row r="21">
@@ -9632,10 +9710,10 @@
         <v>2158.342082859997</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>241.5676041310861</v>
+        <v>1232.231785459806</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>540.0778489397439</v>
+        <v>5447.858316598144</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>1099.200923162125</v>
@@ -9684,6 +9762,12 @@
       </c>
       <c r="V21" s="2" t="n">
         <v>6520.26713364986</v>
+      </c>
+      <c r="W21" t="n">
+        <v>241.5676041310861</v>
+      </c>
+      <c r="X21" t="n">
+        <v>540.0778489397439</v>
       </c>
     </row>
     <row r="22">
@@ -9702,10 +9786,10 @@
         <v>120.7817896937801</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>30.76774703197291</v>
+        <v>85.11227366773437</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>48.36768264048398</v>
+        <v>191.9759405384857</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>101.3461897719826</v>
@@ -9754,6 +9838,12 @@
       </c>
       <c r="V22" s="2" t="n">
         <v>427.2263741739528</v>
+      </c>
+      <c r="W22" t="n">
+        <v>30.76774703197291</v>
+      </c>
+      <c r="X22" t="n">
+        <v>48.36768264048398</v>
       </c>
     </row>
     <row r="23">
@@ -9772,10 +9862,10 @@
         <v>19.83217120809694</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>8.458359569948094</v>
+        <v>15.94585464513671</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>10.6969856978981</v>
+        <v>25.65179271988774</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>23.18361203338521</v>
@@ -9824,6 +9914,12 @@
       </c>
       <c r="V23" s="2" t="n">
         <v>22.47400221473151</v>
+      </c>
+      <c r="W23" t="n">
+        <v>8.458359569948094</v>
+      </c>
+      <c r="X23" t="n">
+        <v>10.6969856978981</v>
       </c>
     </row>
     <row r="24">
@@ -9842,10 +9938,10 @@
         <v>10</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>5.184929654305977</v>
+        <v>8.452571931857362</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>5.184929654305977</v>
+        <v>8.452571931857362</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>16.6073546856465</v>
@@ -9894,6 +9990,12 @@
       </c>
       <c r="V24" s="2" t="n">
         <v>16.08702110561454</v>
+      </c>
+      <c r="W24" t="n">
+        <v>5.184929654305977</v>
+      </c>
+      <c r="X24" t="n">
+        <v>5.184929654305977</v>
       </c>
     </row>
     <row r="25">
@@ -9912,10 +10014,10 @@
         <v>10</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>5.184929654305977</v>
+        <v>8.452571931857362</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>5.184929654305977</v>
+        <v>8.452571931857362</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>8.169934640522877</v>
@@ -9964,6 +10066,12 @@
       </c>
       <c r="V25" s="2" t="n">
         <v>6.553053834101111</v>
+      </c>
+      <c r="W25" t="n">
+        <v>5.184929654305977</v>
+      </c>
+      <c r="X25" t="n">
+        <v>5.184929654305977</v>
       </c>
     </row>
     <row r="26">
@@ -9982,10 +10090,10 @@
         <v>20.38348088905525</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>8.62575987376824</v>
+        <v>16.35635265267133</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>11.53895152441546</v>
+        <v>27.0970148733113</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>31.21224196102762</v>
@@ -10034,6 +10142,12 @@
       </c>
       <c r="V26" s="2" t="n">
         <v>36.12964465806405</v>
+      </c>
+      <c r="W26" t="n">
+        <v>8.625759873768247</v>
+      </c>
+      <c r="X26" t="n">
+        <v>11.53895152441546</v>
       </c>
     </row>
     <row r="27">
@@ -10052,10 +10166,10 @@
         <v>40.59342455332725</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>14.11341897979981</v>
+        <v>30.97565737965035</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>19.25304047531985</v>
+        <v>51.83789221172644</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>55.36298010087616</v>
@@ -10104,6 +10218,12 @@
       </c>
       <c r="V27" s="2" t="n">
         <v>55.59273638010765</v>
+      </c>
+      <c r="W27" t="n">
+        <v>14.11341897979981</v>
+      </c>
+      <c r="X27" t="n">
+        <v>19.25304047531985</v>
       </c>
     </row>
     <row r="28">
@@ -10122,10 +10242,10 @@
         <v>364.0841816236014</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>67.70188004633907</v>
+        <v>236.7039938990796</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>104.3106992097627</v>
+        <v>527.6744033010473</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>247.2339412619332</v>
@@ -10174,6 +10294,12 @@
       </c>
       <c r="V28" s="2" t="n">
         <v>553.5262317609975</v>
+      </c>
+      <c r="W28" t="n">
+        <v>67.70188004633917</v>
+      </c>
+      <c r="X28" t="n">
+        <v>104.3106992097627</v>
       </c>
     </row>
     <row r="29">
@@ -10192,10 +10318,10 @@
         <v>113.3280478898344</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>29.39835378254112</v>
+        <v>80.2320563556564</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>48.66214850859724</v>
+        <v>188.7106537577393</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>114.7411942878243</v>
@@ -10244,6 +10370,12 @@
       </c>
       <c r="V29" s="2" t="n">
         <v>181.4619985274187</v>
+      </c>
+      <c r="W29" t="n">
+        <v>29.39835378254112</v>
+      </c>
+      <c r="X29" t="n">
+        <v>48.66214850859724</v>
       </c>
     </row>
     <row r="30">
@@ -10262,10 +10394,10 @@
         <v>266.3964144838355</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>54.15382144094457</v>
+        <v>177.1894338978233</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>94.03887382835504</v>
+        <v>538.9550495656759</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>238.8108208881494</v>
@@ -10314,6 +10446,12 @@
       </c>
       <c r="V30" s="2" t="n">
         <v>618.8326040733842</v>
+      </c>
+      <c r="W30" t="n">
+        <v>54.1538214409446</v>
+      </c>
+      <c r="X30" t="n">
+        <v>94.03887382835504</v>
       </c>
     </row>
     <row r="31">
@@ -10332,10 +10470,10 @@
         <v>637.4535029361823</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>101.0321451438866</v>
+        <v>397.8254585559248</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>217.2492510098234</v>
+        <v>1648.537339839571</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>624.3448654301847</v>
@@ -10384,6 +10522,12 @@
       </c>
       <c r="V31" s="2" t="n">
         <v>1565.320370022235</v>
+      </c>
+      <c r="W31" t="n">
+        <v>101.0321451438866</v>
+      </c>
+      <c r="X31" t="n">
+        <v>217.2492510098234</v>
       </c>
     </row>
     <row r="32">
@@ -10402,10 +10546,10 @@
         <v>118.3681784784167</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>30.32703173189654</v>
+        <v>83.53447509889496</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>42.11937640103142</v>
+        <v>162.0760342511591</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>97.9995349784746</v>
@@ -10454,6 +10598,12 @@
       </c>
       <c r="V32" s="2" t="n">
         <v>184.6524454998177</v>
+      </c>
+      <c r="W32" t="n">
+        <v>30.32703173189654</v>
+      </c>
+      <c r="X32" t="n">
+        <v>42.11937640103142</v>
       </c>
     </row>
     <row r="33">
@@ -10472,10 +10622,10 @@
         <v>777.4469221274892</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>116.4357387086099</v>
+        <v>478.2110709334553</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>252.3174111939063</v>
+        <v>1910.940460270377</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>650.6900022192285</v>
@@ -10524,6 +10674,12 @@
       </c>
       <c r="V33" s="2" t="n">
         <v>1830.95279402164</v>
+      </c>
+      <c r="W33" t="n">
+        <v>116.43573870861</v>
+      </c>
+      <c r="X33" t="n">
+        <v>252.3174111939063</v>
       </c>
     </row>
     <row r="34">
@@ -10542,10 +10698,10 @@
         <v>1075.664237452001</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>146.8484349764607</v>
+        <v>646.1459137801459</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>324.4621977031346</v>
+        <v>2934.496590346338</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>886.0414223656692</v>
@@ -10594,6 +10750,12 @@
       </c>
       <c r="V34" s="2" t="n">
         <v>2489.119691429056</v>
+      </c>
+      <c r="W34" t="n">
+        <v>146.8484349764607</v>
+      </c>
+      <c r="X34" t="n">
+        <v>324.4621977031346</v>
       </c>
     </row>
     <row r="35">
@@ -10612,10 +10774,10 @@
         <v>10</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>5.184929654305977</v>
+        <v>8.452571931857362</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>5.184929654305977</v>
+        <v>8.452571931857362</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>7.777777777777779</v>
@@ -10664,6 +10826,12 @@
       </c>
       <c r="V35" s="2" t="n">
         <v>7.623828874381004</v>
+      </c>
+      <c r="W35" t="n">
+        <v>5.184929654305977</v>
+      </c>
+      <c r="X35" t="n">
+        <v>5.184929654305977</v>
       </c>
     </row>
     <row r="36">
@@ -10682,10 +10850,10 @@
         <v>10</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>5.184929654305977</v>
+        <v>8.452571931857362</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>5.184929654305977</v>
+        <v>8.452571931857362</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>8.333333333333332</v>
@@ -10734,6 +10902,12 @@
       </c>
       <c r="V36" s="2" t="n">
         <v>6.688861929578463</v>
+      </c>
+      <c r="W36" t="n">
+        <v>5.184929654305977</v>
+      </c>
+      <c r="X36" t="n">
+        <v>5.184929654305977</v>
       </c>
     </row>
     <row r="37">
@@ -10752,10 +10926,10 @@
         <v>20.6913808111479</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>8.718688124385483</v>
+        <v>16.58525695314438</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>11.43525293132934</v>
+        <v>26.92796343467415</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>25.78059027777778</v>
@@ -10804,6 +10978,12 @@
       </c>
       <c r="V37" s="2" t="n">
         <v>39.84173054826182</v>
+      </c>
+      <c r="W37" t="n">
+        <v>8.718688124385483</v>
+      </c>
+      <c r="X37" t="n">
+        <v>11.43525293132934</v>
       </c>
     </row>
     <row r="38">
@@ -10822,10 +11002,10 @@
         <v>291.4626857008921</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>57.74881757295464</v>
+        <v>192.5932174288715</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>95.60984159101858</v>
+        <v>511.4770211652419</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>219.2495656238574</v>
@@ -10874,6 +11054,12 @@
       </c>
       <c r="V38" s="2" t="n">
         <v>565.5388749443975</v>
+      </c>
+      <c r="W38" t="n">
+        <v>57.74881757295464</v>
+      </c>
+      <c r="X38" t="n">
+        <v>95.60984159101858</v>
       </c>
     </row>
     <row r="39">
@@ -10892,10 +11078,10 @@
         <v>102.0689829756418</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>27.27988330690686</v>
+        <v>72.81522447037258</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>41.75721261005104</v>
+        <v>152.8212961197705</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>80.02955980759683</v>
@@ -10944,6 +11130,12 @@
       </c>
       <c r="V39" s="2" t="n">
         <v>158.8915459604862</v>
+      </c>
+      <c r="W39" t="n">
+        <v>27.27988330690686</v>
+      </c>
+      <c r="X39" t="n">
+        <v>41.75721261005104</v>
       </c>
     </row>
     <row r="40">
@@ -10962,10 +11154,10 @@
         <v>531.197087833919</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>88.68640816109608</v>
+        <v>335.955459317536</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>193.1099965183566</v>
+        <v>1587.479007171884</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>1266.70806084563</v>
@@ -11014,6 +11206,12 @@
       </c>
       <c r="V40" s="2" t="n">
         <v>4920.75545845894</v>
+      </c>
+      <c r="W40" t="n">
+        <v>88.68640816109608</v>
+      </c>
+      <c r="X40" t="n">
+        <v>193.1099965183566</v>
       </c>
     </row>
     <row r="41">
@@ -11032,10 +11230,10 @@
         <v>105.6026732411462</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>27.95163468827293</v>
+        <v>75.1491600535318</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>35.15974292236476</v>
+        <v>121.190598650094</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>51.40345223129118</v>
@@ -11084,6 +11282,12 @@
       </c>
       <c r="V41" s="2" t="n">
         <v>115.8247914696551</v>
+      </c>
+      <c r="W41" t="n">
+        <v>27.95163468827293</v>
+      </c>
+      <c r="X41" t="n">
+        <v>35.15974292236476</v>
       </c>
     </row>
     <row r="42">
@@ -11102,10 +11306,10 @@
         <v>603.5344247549335</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>97.15987724186182</v>
+        <v>378.1637212134535</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>222.3183809741709</v>
+        <v>1694.952028581702</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>478.5877085417904</v>
@@ -11154,6 +11358,12 @@
       </c>
       <c r="V42" s="2" t="n">
         <v>2074.294761635988</v>
+      </c>
+      <c r="W42" t="n">
+        <v>97.15987724186182</v>
+      </c>
+      <c r="X42" t="n">
+        <v>222.3183809741709</v>
       </c>
     </row>
     <row r="43">
@@ -11172,10 +11382,10 @@
         <v>916.9279493730987</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>131.0110617283385</v>
+        <v>557.2521919849985</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>296.9497871177057</v>
+        <v>2854.499188992327</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>815.0008099828917</v>
@@ -11224,6 +11434,12 @@
       </c>
       <c r="V43" s="2" t="n">
         <v>3327.71693272612</v>
+      </c>
+      <c r="W43" t="n">
+        <v>131.0110617283384</v>
+      </c>
+      <c r="X43" t="n">
+        <v>296.9497871177057</v>
       </c>
     </row>
     <row r="44">
@@ -11242,10 +11458,10 @@
         <v>308.8909635715052</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>60.19639914752178</v>
+        <v>203.2458680923693</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>159.4386770508756</v>
+        <v>1395.318900906241</v>
       </c>
       <c r="G44" s="2" t="n">
         <v>429.3626786906136</v>
@@ -11294,6 +11510,12 @@
       </c>
       <c r="V44" s="2" t="n">
         <v>1946.758423210331</v>
+      </c>
+      <c r="W44" t="n">
+        <v>60.19639914752178</v>
+      </c>
+      <c r="X44" t="n">
+        <v>159.4386770508756</v>
       </c>
     </row>
     <row r="45">
@@ -11312,10 +11534,10 @@
         <v>99.99999999999999</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>26.88349552010149</v>
+        <v>71.44597226322288</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>26.88349552010149</v>
+        <v>71.44597226322288</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>290.9954946858862</v>
@@ -11364,6 +11586,12 @@
       </c>
       <c r="V45" s="2" t="n">
         <v>292.3357164506814</v>
+      </c>
+      <c r="W45" t="n">
+        <v>26.88349552010149</v>
+      </c>
+      <c r="X45" t="n">
+        <v>26.88349552010149</v>
       </c>
     </row>
     <row r="46">
@@ -11382,10 +11610,10 @@
         <v>990.1195105897258</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>138.4032733648722</v>
+        <v>598.369014548643</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>209.3243902879981</v>
+        <v>1346.233095121702</v>
       </c>
       <c r="G46" s="2" t="n">
         <v>376.9367699410784</v>
@@ -11434,6 +11662,12 @@
       </c>
       <c r="V46" s="2" t="n">
         <v>1512.277541163071</v>
+      </c>
+      <c r="W46" t="n">
+        <v>138.4032733648723</v>
+      </c>
+      <c r="X46" t="n">
+        <v>209.3243902879981</v>
       </c>
     </row>
     <row r="47">
@@ -11452,10 +11686,10 @@
         <v>99.99999999999999</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>26.88349552010149</v>
+        <v>71.44597226322288</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>26.8834955201015</v>
+        <v>71.4459722632229</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>392.8170594837253</v>
@@ -11504,6 +11738,12 @@
       </c>
       <c r="V47" s="2" t="n">
         <v>405.8197911230272</v>
+      </c>
+      <c r="W47" t="n">
+        <v>26.88349552010149</v>
+      </c>
+      <c r="X47" t="n">
+        <v>26.8834955201015</v>
       </c>
     </row>
     <row r="48">
@@ -11522,10 +11762,10 @@
         <v>2151.411916290904</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>241.012964323653</v>
+        <v>1228.563684459247</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>536.3374199998124</v>
+        <v>5446.03564052138</v>
       </c>
       <c r="G48" s="2" t="n">
         <v>1745.73554821722</v>
@@ -11574,6 +11814,12 @@
       </c>
       <c r="V48" s="2" t="n">
         <v>7907.299161633682</v>
+      </c>
+      <c r="W48" t="n">
+        <v>241.012964323653</v>
+      </c>
+      <c r="X48" t="n">
+        <v>536.3374199998124</v>
       </c>
     </row>
     <row r="49">
@@ -11592,10 +11838,10 @@
         <v>3650.332839369454</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>351.6832831106373</v>
+        <v>2005.591894149655</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>848.5746815574474</v>
+        <v>10195.61748859687</v>
       </c>
       <c r="G49" s="2" t="n">
         <v>2102.414307698629</v>
@@ -11644,6 +11890,12 @@
       </c>
       <c r="V49" s="2" t="n">
         <v>11377.13368721327</v>
+      </c>
+      <c r="W49" t="n">
+        <v>351.6832831106373</v>
+      </c>
+      <c r="X49" t="n">
+        <v>848.5746815574474</v>
       </c>
     </row>
     <row r="50">
@@ -11662,10 +11914,10 @@
         <v>1214.104791986036</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>160.1216676518294</v>
+        <v>722.8882426245019</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>657.5450354637417</v>
+        <v>10114.1013381135</v>
       </c>
       <c r="G50" s="2" t="n">
         <v>2494.373459647526</v>
@@ -11715,6 +11967,12 @@
       <c r="V50" s="2" t="n">
         <v>23723.7058082503</v>
       </c>
+      <c r="W50" t="n">
+        <v>160.1216676518297</v>
+      </c>
+      <c r="X50" t="n">
+        <v>657.5450354637417</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -11732,10 +11990,10 @@
         <v>1757.235698011361</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>208.5542836264397</v>
+        <v>1018.406888848657</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>1010.152404325292</v>
+        <v>15262.31096998855</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>5136.373322166427</v>
@@ -11784,6 +12042,12 @@
       </c>
       <c r="V51" s="2" t="n">
         <v>31682.71884742665</v>
+      </c>
+      <c r="W51" t="n">
+        <v>208.5542836264397</v>
+      </c>
+      <c r="X51" t="n">
+        <v>1010.152404325292</v>
       </c>
     </row>
   </sheetData>
@@ -11797,7 +12061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V51"/>
+  <dimension ref="A1:X51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -11935,6 +12199,16 @@
           <t>MC_new_TE_EEfix</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -11984,19 +12258,22 @@
       <c r="O2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="V2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12069,6 +12346,12 @@
       <c r="V3" s="2" t="n">
         <v>0.7954499490366782</v>
       </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -12086,10 +12369,10 @@
         <v>4151.453096259821</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>385.5518078428939</v>
+        <v>2259.598482293819</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1105.841937881627</v>
+        <v>15252.83287640466</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>2733.073309257259</v>
@@ -12138,6 +12421,12 @@
       </c>
       <c r="V4" s="2" t="n">
         <v>12974.66613827684</v>
+      </c>
+      <c r="W4" t="n">
+        <v>385.5518078428939</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1105.841937881627</v>
       </c>
     </row>
     <row r="5">
@@ -12156,10 +12445,10 @@
         <v>7345.100996801307</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>579.6880360264884</v>
+        <v>3834.748855479991</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>954.4728639062726</v>
+        <v>9823.345812148596</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>1880.53027144579</v>
@@ -12208,6 +12497,12 @@
       </c>
       <c r="V5" s="2" t="n">
         <v>7809.894595033291</v>
+      </c>
+      <c r="W5" t="n">
+        <v>579.6880360264884</v>
+      </c>
+      <c r="X5" t="n">
+        <v>954.4728639062726</v>
       </c>
     </row>
     <row r="6">
@@ -12226,10 +12521,10 @@
         <v>2885.425512703825</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>297.276327018125</v>
+        <v>1612.783432435319</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>850.9317555144944</v>
+        <v>11857.37802254126</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>2419.641372518714</v>
@@ -12278,6 +12573,12 @@
       </c>
       <c r="V6" s="2" t="n">
         <v>10228.51584331186</v>
+      </c>
+      <c r="W6" t="n">
+        <v>297.276327018125</v>
+      </c>
+      <c r="X6" t="n">
+        <v>850.9317555144944</v>
       </c>
     </row>
     <row r="7">
@@ -12349,6 +12650,12 @@
       <c r="V7" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -12419,6 +12726,12 @@
       <c r="V8" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -12489,6 +12802,12 @@
       <c r="V9" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -12559,6 +12878,12 @@
       <c r="V10" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -12576,10 +12901,10 @@
         <v>10</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>5.184929654305977</v>
+        <v>8.452571931857362</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>5.184929654305977</v>
+        <v>8.452571931857362</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>7.77777777777778</v>
@@ -12628,6 +12953,12 @@
       </c>
       <c r="V11" s="2" t="n">
         <v>7.830316843609689</v>
+      </c>
+      <c r="W11" t="n">
+        <v>5.184929654305977</v>
+      </c>
+      <c r="X11" t="n">
+        <v>5.184929654305977</v>
       </c>
     </row>
     <row r="12">
@@ -12646,10 +12977,10 @@
         <v>10</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>5.184929654305977</v>
+        <v>8.452571931857362</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>5.184929654305977</v>
+        <v>8.452571931857362</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>7.18390804597701</v>
@@ -12698,6 +13029,12 @@
       </c>
       <c r="V12" s="2" t="n">
         <v>5.775608899396589</v>
+      </c>
+      <c r="W12" t="n">
+        <v>5.184929654305977</v>
+      </c>
+      <c r="X12" t="n">
+        <v>5.184929654305977</v>
       </c>
     </row>
     <row r="13">
@@ -12716,10 +13053,10 @@
         <v>56.2341325190349</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>17.81558222516434</v>
+        <v>41.9015927763331</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>19.07453693658011</v>
+        <v>49.50899749367245</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>36.31482653996292</v>
@@ -12768,6 +13105,12 @@
       </c>
       <c r="V13" s="2" t="n">
         <v>238.6149686923292</v>
+      </c>
+      <c r="W13" t="n">
+        <v>17.81558222516434</v>
+      </c>
+      <c r="X13" t="n">
+        <v>19.07453693658011</v>
       </c>
     </row>
     <row r="14">
@@ -12786,10 +13129,10 @@
         <v>99.99999999999999</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>26.88349552010149</v>
+        <v>71.44597226322288</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>24.64320422675971</v>
+        <v>65.49214124128767</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>47.35384300348653</v>
@@ -12838,6 +13181,12 @@
       </c>
       <c r="V14" s="2" t="n">
         <v>110.0668785531916</v>
+      </c>
+      <c r="W14" t="n">
+        <v>26.88349552010149</v>
+      </c>
+      <c r="X14" t="n">
+        <v>24.64320422675971</v>
       </c>
     </row>
     <row r="15">
@@ -12856,10 +13205,10 @@
         <v>899.5569660715325</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>129.2322560759423</v>
+        <v>547.4591457880141</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>143.8492639193627</v>
+        <v>750.4614609747833</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>230.3646969498067</v>
@@ -12908,6 +13257,12 @@
       </c>
       <c r="V15" s="2" t="n">
         <v>1588.46691280969</v>
+      </c>
+      <c r="W15" t="n">
+        <v>129.2322560759425</v>
+      </c>
+      <c r="X15" t="n">
+        <v>143.8492639193627</v>
       </c>
     </row>
     <row r="16">
@@ -12926,10 +13281,10 @@
         <v>233.2691835057716</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>49.25033267370252</v>
+        <v>156.6669683960035</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>72.64325258102383</v>
+        <v>299.6250848086902</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>120.8448613846694</v>
@@ -12978,6 +13333,12 @@
       </c>
       <c r="V16" s="2" t="n">
         <v>651.8858448464284</v>
+      </c>
+      <c r="W16" t="n">
+        <v>49.25033267370252</v>
+      </c>
+      <c r="X16" t="n">
+        <v>72.64325258102383</v>
       </c>
     </row>
     <row r="17">
@@ -12996,10 +13357,10 @@
         <v>658.0386994075527</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>103.3534825911695</v>
+        <v>409.7205324309327</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>129.9081947060682</v>
+        <v>716.4226049273376</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>260.8366265453813</v>
@@ -13048,6 +13409,12 @@
       </c>
       <c r="V17" s="2" t="n">
         <v>1864.94694959798</v>
+      </c>
+      <c r="W17" t="n">
+        <v>103.3534825911695</v>
+      </c>
+      <c r="X17" t="n">
+        <v>129.9081947060682</v>
       </c>
     </row>
     <row r="18">
@@ -13066,10 +13433,10 @@
         <v>1222.123215826166</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>160.8768027173467</v>
+        <v>727.3128429368896</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>313.8338821862761</v>
+        <v>2580.026511114823</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>655.1439238833415</v>
@@ -13118,6 +13485,12 @@
       </c>
       <c r="V18" s="2" t="n">
         <v>4026.144563833815</v>
+      </c>
+      <c r="W18" t="n">
+        <v>160.8768027173467</v>
+      </c>
+      <c r="X18" t="n">
+        <v>313.8338821862761</v>
       </c>
     </row>
     <row r="19">
@@ -13136,10 +13509,10 @@
         <v>149.3209864750716</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>35.80448020290444</v>
+        <v>103.6062230671559</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>51.08046009975313</v>
+        <v>205.6415282537541</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>73.62307377068427</v>
@@ -13188,6 +13561,12 @@
       </c>
       <c r="V19" s="2" t="n">
         <v>347.7505741447178</v>
+      </c>
+      <c r="W19" t="n">
+        <v>35.80448020290444</v>
+      </c>
+      <c r="X19" t="n">
+        <v>51.08046009975313</v>
       </c>
     </row>
     <row r="20">
@@ -13206,10 +13585,10 @@
         <v>1165.755227118985</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>155.5377275061178</v>
+        <v>696.1629693121913</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>312.2486659981944</v>
+        <v>2381.019565852759</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>636.774095292947</v>
@@ -13258,6 +13637,12 @@
       </c>
       <c r="V20" s="2" t="n">
         <v>3353.957227116678</v>
+      </c>
+      <c r="W20" t="n">
+        <v>155.5377275061178</v>
+      </c>
+      <c r="X20" t="n">
+        <v>312.2486659981944</v>
       </c>
     </row>
     <row r="21">
@@ -13276,10 +13661,10 @@
         <v>2158.342082859997</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>241.5676041310861</v>
+        <v>1232.231785459806</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>540.7685021374374</v>
+        <v>5451.424139393699</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>1099.737997453578</v>
@@ -13328,6 +13713,12 @@
       </c>
       <c r="V21" s="2" t="n">
         <v>6521.240852133582</v>
+      </c>
+      <c r="W21" t="n">
+        <v>241.5676041310861</v>
+      </c>
+      <c r="X21" t="n">
+        <v>540.7685021374374</v>
       </c>
     </row>
     <row r="22">
@@ -13346,10 +13737,10 @@
         <v>120.7817896937801</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>30.76774703197291</v>
+        <v>85.11227366773437</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>48.42692305803595</v>
+        <v>192.1465286352705</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>101.3955596704835</v>
@@ -13398,6 +13789,12 @@
       </c>
       <c r="V22" s="2" t="n">
         <v>427.2868770219175</v>
+      </c>
+      <c r="W22" t="n">
+        <v>30.76774703197291</v>
+      </c>
+      <c r="X22" t="n">
+        <v>48.42692305803595</v>
       </c>
     </row>
     <row r="23">
@@ -13416,10 +13813,10 @@
         <v>19.83217120809694</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>8.458359569948094</v>
+        <v>15.94585464513671</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>11.6374378919698</v>
+        <v>27.18493595400325</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>23.95957721761544</v>
@@ -13468,6 +13865,12 @@
       </c>
       <c r="V23" s="2" t="n">
         <v>23.24683168863488</v>
+      </c>
+      <c r="W23" t="n">
+        <v>8.458359569948094</v>
+      </c>
+      <c r="X23" t="n">
+        <v>11.6374378919698</v>
       </c>
     </row>
     <row r="24">
@@ -13486,10 +13889,10 @@
         <v>10</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>5.184929654305977</v>
+        <v>8.452571931857362</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>5.184929654305977</v>
+        <v>8.452571931857362</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>16.6073546856465</v>
@@ -13538,6 +13941,12 @@
       </c>
       <c r="V24" s="2" t="n">
         <v>16.08702110561454</v>
+      </c>
+      <c r="W24" t="n">
+        <v>5.184929654305977</v>
+      </c>
+      <c r="X24" t="n">
+        <v>5.184929654305977</v>
       </c>
     </row>
     <row r="25">
@@ -13556,10 +13965,10 @@
         <v>10</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>5.184929654305977</v>
+        <v>8.452571931857362</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>5.184929654305977</v>
+        <v>8.452571931857362</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>8.169934640522877</v>
@@ -13608,6 +14017,12 @@
       </c>
       <c r="V25" s="2" t="n">
         <v>6.553053834101111</v>
+      </c>
+      <c r="W25" t="n">
+        <v>5.184929654305977</v>
+      </c>
+      <c r="X25" t="n">
+        <v>5.184929654305977</v>
       </c>
     </row>
     <row r="26">
@@ -13626,10 +14041,10 @@
         <v>20.38348088905525</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>8.62575987376824</v>
+        <v>16.35635265267133</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>11.53895152441546</v>
+        <v>27.0970148733113</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>31.21224196102762</v>
@@ -13678,6 +14093,12 @@
       </c>
       <c r="V26" s="2" t="n">
         <v>36.12964465806405</v>
+      </c>
+      <c r="W26" t="n">
+        <v>8.625759873768247</v>
+      </c>
+      <c r="X26" t="n">
+        <v>11.53895152441546</v>
       </c>
     </row>
     <row r="27">
@@ -13696,10 +14117,10 @@
         <v>40.59342455332725</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>14.11341897979981</v>
+        <v>30.97565737965035</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>19.25304047531985</v>
+        <v>51.83789221172644</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>55.36298010087616</v>
@@ -13748,6 +14169,12 @@
       </c>
       <c r="V27" s="2" t="n">
         <v>55.59273638010765</v>
+      </c>
+      <c r="W27" t="n">
+        <v>14.11341897979981</v>
+      </c>
+      <c r="X27" t="n">
+        <v>19.25304047531985</v>
       </c>
     </row>
     <row r="28">
@@ -13766,10 +14193,10 @@
         <v>364.0841816236014</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>67.70188004633907</v>
+        <v>236.7039938990796</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>104.4395945896435</v>
+        <v>528.0919828074306</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>247.3155935666693</v>
@@ -13818,6 +14245,12 @@
       </c>
       <c r="V28" s="2" t="n">
         <v>553.6745360287654</v>
+      </c>
+      <c r="W28" t="n">
+        <v>67.70188004633917</v>
+      </c>
+      <c r="X28" t="n">
+        <v>104.4395945896435</v>
       </c>
     </row>
     <row r="29">
@@ -13836,10 +14269,10 @@
         <v>113.3280478898344</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>29.39835378254112</v>
+        <v>80.2320563556564</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>48.68014179787855</v>
+        <v>188.7543964031884</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>114.7539911746019</v>
@@ -13888,6 +14321,12 @@
       </c>
       <c r="V29" s="2" t="n">
         <v>181.4903625831807</v>
+      </c>
+      <c r="W29" t="n">
+        <v>29.39835378254112</v>
+      </c>
+      <c r="X29" t="n">
+        <v>48.68014179787855</v>
       </c>
     </row>
     <row r="30">
@@ -13906,10 +14345,10 @@
         <v>266.3964144838355</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>54.15382144094457</v>
+        <v>177.1894338978233</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>94.18468263694609</v>
+        <v>539.4157032861734</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>238.9273692143364</v>
@@ -13958,6 +14397,12 @@
       </c>
       <c r="V30" s="2" t="n">
         <v>619.0150630708874</v>
+      </c>
+      <c r="W30" t="n">
+        <v>54.1538214409446</v>
+      </c>
+      <c r="X30" t="n">
+        <v>94.18468263694609</v>
       </c>
     </row>
     <row r="31">
@@ -13976,10 +14421,10 @@
         <v>637.4535029361823</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>101.0321451438866</v>
+        <v>397.8254585559248</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>217.5020378006488</v>
+        <v>1649.741779711355</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>624.5346615437196</v>
@@ -14028,6 +14473,12 @@
       </c>
       <c r="V31" s="2" t="n">
         <v>1565.693449370743</v>
+      </c>
+      <c r="W31" t="n">
+        <v>101.0321451438866</v>
+      </c>
+      <c r="X31" t="n">
+        <v>217.5020378006488</v>
       </c>
     </row>
     <row r="32">
@@ -14046,10 +14497,10 @@
         <v>118.3681784784167</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>30.32703173189654</v>
+        <v>83.53447509889496</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>42.19981775260638</v>
+        <v>162.2968292418566</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>98.0533624621678</v>
@@ -14098,6 +14549,12 @@
       </c>
       <c r="V32" s="2" t="n">
         <v>184.7297433324445</v>
+      </c>
+      <c r="W32" t="n">
+        <v>30.32703173189654</v>
+      </c>
+      <c r="X32" t="n">
+        <v>42.19981775260638</v>
       </c>
     </row>
     <row r="33">
@@ -14116,10 +14573,10 @@
         <v>777.4469221274892</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>116.4357387086099</v>
+        <v>478.2110709334553</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>252.8150782093971</v>
+        <v>1912.817433181032</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>651.0792050986457</v>
@@ -14168,6 +14625,12 @@
       </c>
       <c r="V33" s="2" t="n">
         <v>1831.550700289293</v>
+      </c>
+      <c r="W33" t="n">
+        <v>116.43573870861</v>
+      </c>
+      <c r="X33" t="n">
+        <v>252.8150782093971</v>
       </c>
     </row>
     <row r="34">
@@ -14186,10 +14649,10 @@
         <v>1075.664237452001</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>146.8484349764607</v>
+        <v>646.1459137801459</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>324.9909366125136</v>
+        <v>2936.979378535357</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>886.4577870092359</v>
@@ -14238,6 +14701,12 @@
       </c>
       <c r="V34" s="2" t="n">
         <v>2489.790959942448</v>
+      </c>
+      <c r="W34" t="n">
+        <v>146.8484349764607</v>
+      </c>
+      <c r="X34" t="n">
+        <v>324.9909366125136</v>
       </c>
     </row>
     <row r="35">
@@ -14256,10 +14725,10 @@
         <v>10</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>5.184929654305977</v>
+        <v>8.452571931857362</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>5.184929654305977</v>
+        <v>8.452571931857362</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>7.777777777777779</v>
@@ -14308,6 +14777,12 @@
       </c>
       <c r="V35" s="2" t="n">
         <v>7.623828874381004</v>
+      </c>
+      <c r="W35" t="n">
+        <v>5.184929654305977</v>
+      </c>
+      <c r="X35" t="n">
+        <v>5.184929654305977</v>
       </c>
     </row>
     <row r="36">
@@ -14326,10 +14801,10 @@
         <v>10</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>5.184929654305977</v>
+        <v>8.452571931857362</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>5.184929654305977</v>
+        <v>8.452571931857362</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>8.333333333333332</v>
@@ -14378,6 +14853,12 @@
       </c>
       <c r="V36" s="2" t="n">
         <v>6.688861929578463</v>
+      </c>
+      <c r="W36" t="n">
+        <v>5.184929654305977</v>
+      </c>
+      <c r="X36" t="n">
+        <v>5.184929654305977</v>
       </c>
     </row>
     <row r="37">
@@ -14396,10 +14877,10 @@
         <v>20.6913808111479</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>8.718688124385483</v>
+        <v>16.58525695314438</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>11.43525293132934</v>
+        <v>26.92796343467415</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>25.78059027777778</v>
@@ -14448,6 +14929,12 @@
       </c>
       <c r="V37" s="2" t="n">
         <v>39.84173054826182</v>
+      </c>
+      <c r="W37" t="n">
+        <v>8.718688124385483</v>
+      </c>
+      <c r="X37" t="n">
+        <v>11.43525293132934</v>
       </c>
     </row>
     <row r="38">
@@ -14466,10 +14953,10 @@
         <v>291.4626857008921</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>57.74881757295464</v>
+        <v>192.5932174288715</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>95.62195803623749</v>
+        <v>511.5435384464595</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>219.2556563314621</v>
@@ -14518,6 +15005,12 @@
       </c>
       <c r="V38" s="2" t="n">
         <v>565.5631398133943</v>
+      </c>
+      <c r="W38" t="n">
+        <v>57.74881757295464</v>
+      </c>
+      <c r="X38" t="n">
+        <v>95.62195803623749</v>
       </c>
     </row>
     <row r="39">
@@ -14536,10 +15029,10 @@
         <v>102.0689829756418</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>27.27988330690686</v>
+        <v>72.81522447037258</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>41.76239546656275</v>
+        <v>152.8297453120255</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>80.03376865037549</v>
@@ -14588,6 +15081,12 @@
       </c>
       <c r="V39" s="2" t="n">
         <v>158.898851782869</v>
+      </c>
+      <c r="W39" t="n">
+        <v>27.27988330690686</v>
+      </c>
+      <c r="X39" t="n">
+        <v>41.76239546656275</v>
       </c>
     </row>
     <row r="40">
@@ -14606,10 +15105,10 @@
         <v>531.197087833919</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>88.68640816109608</v>
+        <v>335.955459317536</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>193.163300820348</v>
+        <v>1587.895094820316</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>1266.790291468621</v>
@@ -14658,6 +15157,12 @@
       </c>
       <c r="V40" s="2" t="n">
         <v>4921.105245488921</v>
+      </c>
+      <c r="W40" t="n">
+        <v>88.68640816109608</v>
+      </c>
+      <c r="X40" t="n">
+        <v>193.163300820348</v>
       </c>
     </row>
     <row r="41">
@@ -14676,10 +15181,10 @@
         <v>105.6026732411462</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>27.95163468827293</v>
+        <v>75.1491600535318</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>35.16079328563669</v>
+        <v>121.1928575201381</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>51.4042240141431</v>
@@ -14728,6 +15233,12 @@
       </c>
       <c r="V41" s="2" t="n">
         <v>115.8276637602536</v>
+      </c>
+      <c r="W41" t="n">
+        <v>27.95163468827293</v>
+      </c>
+      <c r="X41" t="n">
+        <v>35.16079328563669</v>
       </c>
     </row>
     <row r="42">
@@ -14746,10 +15257,10 @@
         <v>603.5344247549335</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>97.15987724186182</v>
+        <v>378.1637212134535</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>222.3821323636273</v>
+        <v>1695.370039303069</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>478.6223099214828</v>
@@ -14798,6 +15309,12 @@
       </c>
       <c r="V42" s="2" t="n">
         <v>2074.440101797484</v>
+      </c>
+      <c r="W42" t="n">
+        <v>97.15987724186182</v>
+      </c>
+      <c r="X42" t="n">
+        <v>222.3821323636273</v>
       </c>
     </row>
     <row r="43">
@@ -14816,10 +15333,10 @@
         <v>916.9279493730987</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>131.0110617283385</v>
+        <v>557.2521919849985</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>297.0742331957993</v>
+        <v>2855.514991810351</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>815.0869613726061</v>
@@ -14868,6 +15385,12 @@
       </c>
       <c r="V43" s="2" t="n">
         <v>3327.999359752639</v>
+      </c>
+      <c r="W43" t="n">
+        <v>131.0110617283384</v>
+      </c>
+      <c r="X43" t="n">
+        <v>297.0742331957993</v>
       </c>
     </row>
     <row r="44">
@@ -14886,10 +15409,10 @@
         <v>308.8909635715052</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>60.19639914752178</v>
+        <v>203.2458680923693</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>159.5579557219373</v>
+        <v>1395.995485908315</v>
       </c>
       <c r="G44" s="2" t="n">
         <v>429.4527340898276</v>
@@ -14938,6 +15461,12 @@
       </c>
       <c r="V44" s="2" t="n">
         <v>1946.997287704122</v>
+      </c>
+      <c r="W44" t="n">
+        <v>60.19639914752178</v>
+      </c>
+      <c r="X44" t="n">
+        <v>159.5579557219373</v>
       </c>
     </row>
     <row r="45">
@@ -14956,10 +15485,10 @@
         <v>99.99999999999999</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>26.88349552010149</v>
+        <v>71.44597226322288</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>26.88349552010149</v>
+        <v>71.44597226322288</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>290.9954946858862</v>
@@ -15008,6 +15537,12 @@
       </c>
       <c r="V45" s="2" t="n">
         <v>292.3357164506814</v>
+      </c>
+      <c r="W45" t="n">
+        <v>26.88349552010149</v>
+      </c>
+      <c r="X45" t="n">
+        <v>26.88349552010149</v>
       </c>
     </row>
     <row r="46">
@@ -15026,10 +15561,10 @@
         <v>990.1195105897258</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>138.4032733648722</v>
+        <v>598.369014548643</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>209.479830750288</v>
+        <v>1346.888416118742</v>
       </c>
       <c r="G46" s="2" t="n">
         <v>377.0162052871622</v>
@@ -15078,6 +15613,12 @@
       </c>
       <c r="V46" s="2" t="n">
         <v>1512.449191321435</v>
+      </c>
+      <c r="W46" t="n">
+        <v>138.4032733648723</v>
+      </c>
+      <c r="X46" t="n">
+        <v>209.479830750288</v>
       </c>
     </row>
     <row r="47">
@@ -15096,10 +15637,10 @@
         <v>99.99999999999999</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>26.88349552010149</v>
+        <v>71.44597226322288</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>26.8834955201015</v>
+        <v>71.4459722632229</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>392.8170594837253</v>
@@ -15148,6 +15689,12 @@
       </c>
       <c r="V47" s="2" t="n">
         <v>405.8197911230272</v>
+      </c>
+      <c r="W47" t="n">
+        <v>26.88349552010149</v>
+      </c>
+      <c r="X47" t="n">
+        <v>26.8834955201015</v>
       </c>
     </row>
     <row r="48">
@@ -15166,10 +15713,10 @@
         <v>2151.411916290904</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>241.012964323653</v>
+        <v>1228.563684459247</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>536.9747675089127</v>
+        <v>5449.628125699543</v>
       </c>
       <c r="G48" s="2" t="n">
         <v>1746.48162340696</v>
@@ -15218,6 +15765,12 @@
       </c>
       <c r="V48" s="2" t="n">
         <v>7908.520492999541</v>
+      </c>
+      <c r="W48" t="n">
+        <v>241.012964323653</v>
+      </c>
+      <c r="X48" t="n">
+        <v>536.9747675089127</v>
       </c>
     </row>
     <row r="49">
@@ -15236,10 +15789,10 @@
         <v>3650.332839369454</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>351.6832831106373</v>
+        <v>2005.591894149655</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>849.6401298009088</v>
+        <v>10202.43918966655</v>
       </c>
       <c r="G49" s="2" t="n">
         <v>2103.316702948289</v>
@@ -15288,6 +15841,12 @@
       </c>
       <c r="V49" s="2" t="n">
         <v>11378.9637723552</v>
+      </c>
+      <c r="W49" t="n">
+        <v>351.6832831106373</v>
+      </c>
+      <c r="X49" t="n">
+        <v>849.6401298009088</v>
       </c>
     </row>
     <row r="50">
@@ -15306,10 +15865,10 @@
         <v>1214.104791986036</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>160.1216676518294</v>
+        <v>722.8882426245019</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>658.771559967749</v>
+        <v>10121.43539815192</v>
       </c>
       <c r="G50" s="2" t="n">
         <v>2496.053381921595</v>
@@ -15359,6 +15918,12 @@
       <c r="V50" s="2" t="n">
         <v>23728.58232104696</v>
       </c>
+      <c r="W50" t="n">
+        <v>160.1216676518297</v>
+      </c>
+      <c r="X50" t="n">
+        <v>658.771559967749</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -15376,10 +15941,10 @@
         <v>1757.235698011361</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>208.5542836264397</v>
+        <v>1018.406888848657</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>1011.467389280642</v>
+        <v>15272.44823356531</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>5138.664286734095</v>
@@ -15428,6 +15993,12 @@
       </c>
       <c r="V51" s="2" t="n">
         <v>31688.00968189066</v>
+      </c>
+      <c r="W51" t="n">
+        <v>208.5542836264397</v>
+      </c>
+      <c r="X51" t="n">
+        <v>1011.467389280642</v>
       </c>
     </row>
   </sheetData>
@@ -15899,7 +16470,6 @@
           <t>WARN</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
       <c r="AD2" s="2" t="n">
         <v>0.3145061031202901</v>
       </c>
@@ -16025,7 +16595,6 @@
       <c r="H3" t="b">
         <v>0</v>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>Bay_of_Bengal (1978)</t>
@@ -16089,7 +16658,6 @@
           <t>WARN</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
       <c r="AD3" s="2" t="n">
         <v>0</v>
       </c>
@@ -16283,7 +16851,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
       <c r="AD4" s="2" t="n">
         <v>0.4125579735832401</v>
       </c>
@@ -16385,7 +16952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -16446,14 +17013,12 @@
       <c r="C2" s="2" t="n">
         <v>283.7293838428675</v>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" s="2" t="n">
         <v>1882.0175611</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0.1507580958368069</v>
       </c>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -16467,14 +17032,12 @@
       <c r="C3" s="2" t="n">
         <v>663.5670471554495</v>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" s="2" t="n">
         <v>1882.0175611</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0.3525828137159402</v>
       </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -16483,19 +17046,17 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>90.19337795021337</v>
+        <v>394.7120701290334</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>90.19337795021337</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
+        <v>394.7120701290334</v>
+      </c>
       <c r="E4" s="2" t="n">
         <v>1882.0175611</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.04792377064616614</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
+        <v>0.2097281546609652</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -16504,22 +17065,22 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>192.5986115828733</v>
+        <v>1836.35925539601</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>192.3262205314893</v>
+        <v>1835.060708407776</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>79.88311224340494</v>
+        <v>710.9708309073544</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>1882.0175611</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.1021915121871013</v>
+        <v>0.9750497266004368</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.04244546591622392</v>
+        <v>0.3777705615519372</v>
       </c>
     </row>
     <row r="6">
@@ -16920,6 +17481,50 @@
       </c>
       <c r="G21" s="2" t="n">
         <v>0.6982127307759647</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>90.1933779502134</v>
+      </c>
+      <c r="C22" t="n">
+        <v>90.1933779502134</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1882.0175611</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.04792377064616615</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>192.5986115828733</v>
+      </c>
+      <c r="C23" t="n">
+        <v>192.3262205314893</v>
+      </c>
+      <c r="D23" t="n">
+        <v>79.88311224340494</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1882.0175611</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.1021915121871013</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.04244546591622392</v>
       </c>
     </row>
   </sheetData>
@@ -17055,7 +17660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -17091,7 +17696,6 @@
           <t>NaN means not available, never zero. A basal source a method does not resolve is NaN, and a method that raised leaves its entire block NaN.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -17104,7 +17708,6 @@
           <t>sppr_all, sppr_inner and sppr_PP are the same table under three source scopes, mirroring get_PPR: sppr_all sums every basal source, sppr_inner drops Import, and sppr_PP drops Import and Detritus. Each is a flat groups x methods table -- rows are group seq with the group name in the first column, one column per method, no MultiIndex. Sums are taken over each method's own basal-source columns before aggregation; the per-source breakdown itself is not written to the workbook.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -17117,7 +17720,6 @@
           <t>SPPR_1986 and SPPR_1995 return one un-attributed SPPR column, so their value cannot be split into a PP-only part: they are NaN in sppr_PP (and in ppr_pp_only) while sppr_inner and sppr_all carry the total. A method that resolves no Detritus source (SPPR_2015) has sppr_inner equal to sppr_PP by construction.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -17130,7 +17732,6 @@
           <t>SPPR_2015() has no only_pp_det parameter (only_pp belongs to get_PPR / get_PPR2NPP_ratio). It is called bare here and PP-only filtering is applied downstream at the get_PPR layer, which is what the ppr_pp_only column and SUM_PP already do.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -17143,7 +17744,6 @@
           <t>Under det_open_mode='none' det_theta does not affect the recycling gain b at all (verified: identical b at theta = 1, 3 and 10). Do not read the health sheet as a theta sensitivity.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -17156,7 +17756,6 @@
           <t>MC runs use exclude_diverged=True, so draws graded FAIL on divergence are dropped as well as draws with a negative SPPR. The two are often the same draws rather than additive -- see the mc_diagnostics sheet for the split by cause.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -17169,7 +17768,6 @@
           <t>SPPR_EwE and the Monte-Carlo methods are called with silent=True rather than silent=False: PPRCalculator imports tqdm.notebook, whose bar needs ipywidgets and raises ImportError('IProgress not found') outside Jupyter, which makes those methods fail outright in a terminal run. Nothing is lost -- this exporter has its own progress bar, and the MC rejection counts appear in mc_diagnostics and in the run report.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -17182,7 +17780,6 @@
           <t>diagnose_sppr grades a CONFIGURATION, not a model: a model can be healthy under one TE_option and divergent under another. Read each row with its config_ columns.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -17195,7 +17792,6 @@
           <t>Every SPPR method, and every diagnose_sppr row, runs in a worker process with a wall-clock budget (180 s by default; --timeout SECONDS on the command line, method_timeout= from Python, and None or 0 to disable it). A method still running when the budget expires is killed and left NaN, exactly like a method that raised -- the status column of this sheet and the run report are the only places that say which of the two happened. A timeout is a statement about this machine and this model, not about the method: rerun it with a larger budget before reading anything into it.</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -17239,7 +17835,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Christensen &amp; Pauly (1995): per-group TE^(1-TL) with global_TE='mean'.</t>
+          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE='mean'. Arithmetic mean with consumer consumption weights.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -17256,7 +17852,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nullspace form of the EwE path sum, global TE at the true mean (Jensen-able on TL).</t>
+          <t>Nullspace form of the EwE path sum, global TE at the consumer consumption-weighted arithmetic mean (Jensen-able on TL).</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -17532,6 +18128,40 @@
         </is>
       </c>
       <c r="C30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>method: SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE='mean'. Arithmetic mean with consumer catch weights. Consumer biomass fallback when consumer catch is zero.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>method: Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Nullspace form of the EwE path sum, global TE at the consumer catch-weighted arithmetic mean. Consumer biomass fallback when consumer catch is zero (Jensen-able on TL).</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
